--- a/artfynd/A 23924-2026 artfynd.xlsx
+++ b/artfynd/A 23924-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY86"/>
+  <dimension ref="A1:AZ86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134529417</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134529402</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1005,6 +1020,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134529403</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1121,6 +1141,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134529404</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1237,6 +1262,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134529405</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1353,6 +1383,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134529406</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1469,6 +1504,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134529407</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1585,6 +1625,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134529408</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1701,6 +1746,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134529418</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1817,6 +1867,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134529419</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1933,6 +1988,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134529421</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2040,6 +2100,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134529427</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2147,6 +2212,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134529433</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2263,6 +2333,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134529813</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2379,6 +2454,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134529822</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2486,6 +2566,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134529393</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2593,6 +2678,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134529394</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2700,6 +2790,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134529395</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2807,6 +2902,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134529397</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2914,6 +3014,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134529400</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3021,6 +3126,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134529401</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3128,6 +3238,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134529411</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3235,6 +3350,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134529412</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3342,6 +3462,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134529415</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3449,6 +3574,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134529416</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3556,6 +3686,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134529420</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3663,6 +3798,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134529424</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3770,6 +3910,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134529425</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3877,6 +4022,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134529428</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3984,6 +4134,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134529436</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4091,6 +4246,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134529438</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4198,6 +4358,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134529779</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4305,6 +4470,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134529780</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4412,6 +4582,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134529782</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4519,6 +4694,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134529783</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4626,6 +4806,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134529784</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4733,6 +4918,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134529787</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4840,6 +5030,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134529789</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4947,6 +5142,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134529790</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5054,6 +5254,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134529791</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5161,6 +5366,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134529794</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5268,6 +5478,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134529796</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5375,6 +5590,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134529797</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5482,6 +5702,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134529799</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5589,6 +5814,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134529800</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5696,6 +5926,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134529807</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5803,6 +6038,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134529808</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5910,6 +6150,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134529811</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6017,6 +6262,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134529812</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6124,6 +6374,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134529816</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6231,6 +6486,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134529817</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6338,6 +6598,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134529819</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6445,6 +6710,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134529820</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6552,6 +6822,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134529821</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6659,6 +6934,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134529396</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6766,6 +7046,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134529409</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6873,6 +7158,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134529423</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6980,6 +7270,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134529430</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7087,6 +7382,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134529431</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7194,6 +7494,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134529435</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7301,6 +7606,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134529439</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7408,6 +7718,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134529792</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7515,6 +7830,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134529809</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7622,6 +7942,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134529804</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7729,6 +8054,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134529413</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7846,6 +8176,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134529392</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7963,6 +8298,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134529398</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8080,6 +8420,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134529399</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8197,6 +8542,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134529414</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8314,6 +8664,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134529426</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8431,6 +8786,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134529429</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8543,6 +8903,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134529781</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8655,6 +9020,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134529786</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8767,6 +9137,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134529788</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8879,6 +9254,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134529798</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8991,6 +9371,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134529805</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -9103,6 +9488,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134529815</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9215,6 +9605,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134529818</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9322,6 +9717,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134529410</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9429,6 +9829,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134529422</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9536,6 +9941,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134529434</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9643,6 +10053,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134529793</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9750,6 +10165,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134529810</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9862,6 +10282,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134529802</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9969,8 +10394,100 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134529806</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>